--- a/seteuk/data/문장은행_기본.xlsx
+++ b/seteuk/data/문장은행_기본.xlsx
@@ -133,10 +133,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -168,10 +168,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -410,6 +410,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A15"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="110"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -481,6 +484,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I112"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="12"/>
+    <col min="2" max="2" customWidth="1" width="26"/>
+    <col min="3" max="3" customWidth="1" width="10"/>
+    <col min="4" max="4" customWidth="1" width="10"/>
+    <col min="5" max="5" customWidth="1" width="8"/>
+    <col min="6" max="6" customWidth="1" width="90"/>
+    <col min="7" max="7" customWidth="1" width="8"/>
+    <col min="8" max="8" customWidth="1" width="22"/>
+    <col min="9" max="9" customWidth="1" width="22"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3741,29 +3755,30 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:V12"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" customWidth="1"/>
-    <col min="2" max="2" width="9.83203125" customWidth="1"/>
-    <col min="3" max="3" width="6.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="24.83203125" customWidth="1"/>
-    <col min="7" max="7" width="5.83203125" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" customWidth="1"/>
-    <col min="9" max="9" width="6.83203125" customWidth="1"/>
-    <col min="10" max="10" width="45.83203125" customWidth="1"/>
-    <col min="11" max="11" width="35.83203125" customWidth="1"/>
-    <col min="12" max="12" width="60.83203125" customWidth="1"/>
-    <col min="13" max="13" width="40.83203125" customWidth="1"/>
-    <col min="14" max="14" width="26.83203125" customWidth="1"/>
-    <col min="15" max="15" width="40.83203125" customWidth="1"/>
-    <col min="16" max="16" width="20.83203125" customWidth="1"/>
-    <col min="17" max="17" width="55.83203125" customWidth="1"/>
-    <col min="18" max="18" width="70.83203125" customWidth="1"/>
-    <col min="19" max="19" width="18.83203125" customWidth="1"/>
-    <col min="20" max="20" width="6.83203125" customWidth="1"/>
-    <col min="21" max="21" width="15.83203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="6.83203125"/>
+    <col min="2" max="2" customWidth="1" width="9.83203125"/>
+    <col min="3" max="3" customWidth="1" width="6.83203125"/>
+    <col min="4" max="4" customWidth="1" width="18.83203125"/>
+    <col min="5" max="5" customWidth="1" width="16.83203125"/>
+    <col min="6" max="6" customWidth="1" width="24.83203125"/>
+    <col min="7" max="7" customWidth="1" width="5.83203125"/>
+    <col min="8" max="8" customWidth="1" width="6.83203125"/>
+    <col min="9" max="9" customWidth="1" width="6.83203125"/>
+    <col min="10" max="10" customWidth="1" width="45.83203125"/>
+    <col min="11" max="11" customWidth="1" width="34.83203125"/>
+    <col min="12" max="12" customWidth="1" width="35.83203125"/>
+    <col min="13" max="13" customWidth="1" width="60.83203125"/>
+    <col min="14" max="14" customWidth="1" width="40.83203125"/>
+    <col min="15" max="15" customWidth="1" width="26.83203125"/>
+    <col min="16" max="16" customWidth="1" width="40.83203125"/>
+    <col min="17" max="17" customWidth="1" width="20.83203125"/>
+    <col min="18" max="18" customWidth="1" width="55.83203125"/>
+    <col min="19" max="19" customWidth="1" width="70.83203125"/>
+    <col min="20" max="20" customWidth="1" width="18.83203125"/>
+    <col min="21" max="21" customWidth="1" width="6.83203125"/>
+    <col min="22" max="22" customWidth="1" width="15.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3798,36 +3813,39 @@
         <v>문제 요약</v>
       </c>
       <c r="K1" t="str">
+        <v>주제 구</v>
+      </c>
+      <c r="L1" t="str">
         <v>핵심 개념</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>풀이 핵심 전략</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>어려운 지점</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>성취기준 코드</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>성취수준 근거</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>교과 역량</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>발표 시 드러나는 행동</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>세특 문장 예시</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <v>정답(검산)</v>
       </c>
-      <c r="T1" t="str">
+      <c r="U1" t="str">
         <v>검토</v>
       </c>
-      <c r="U1" t="str">
+      <c r="V1" t="str">
         <v>비고</v>
       </c>
     </row>
@@ -3863,36 +3881,39 @@
         <v>분자는 이차식, 분모는 절댓값 식인 분수함수에서 x가 2로 갈 때 극한을 조사하는 문제</v>
       </c>
       <c r="K2" t="str">
+        <v>절댓값이 포함된 분수함수의 좌극한과 우극한 조사</v>
+      </c>
+      <c r="L2" t="str">
         <v>좌극한과 우극한, 절댓값 기호의 처리, 인수분해</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>분자를 (x-2)(x-3)으로 인수분해 → x&gt;2, x&lt;2로 나누어 절댓값을 풂 → 우극한 -1, 좌극한 1이 달라 극한이 존재하지 않음을 판단</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>절댓값 안의 부호에 따라 경우를 나누는 것, 좌우극한이 다르면 극한이 없다는 판단 근거 제시</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>12미적Ⅰ-01-01, 12미적Ⅰ-01-02</v>
       </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
         <v>B: 극한의 뜻을 이해하고 주어진 조건에서 좌극한·우극한을 구해 극한의 존재를 판단함</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
         <v>추론, 의사소통</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="R2" t="str">
         <v>절댓값을 경우로 나누어 좌극한과 우극한을 각각 계산함; 두 값이 다르므로 극한이 존재하지 않음을 근거를 들어 설명함</v>
       </c>
-      <c r="R2" t="str">
+      <c r="S2" t="str">
         <v>절댓값이 포함된 함수의 극한을 구간을 나누어 좌극한과 우극한으로 각각 계산하고, 두 값이 달라 극한이 존재하지 않음을 근거를 들어 설명함.</v>
       </c>
-      <c r="S2" t="str">
+      <c r="T2" t="str">
         <v>우극한 -1, 좌극한 1 → 극한 없음</v>
       </c>
-      <c r="T2" t="str">
-        <v/>
-      </c>
       <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
         <v/>
       </c>
     </row>
@@ -3928,36 +3949,39 @@
         <v>x=1을 경계로 식이 다른 함수에서 x가 1로 갈 때 극한이 존재하도록 미정계수를 정하는 문제</v>
       </c>
       <c r="K3" t="str">
+        <v>구간별로 정의된 함수의 극한이 존재할 조건</v>
+      </c>
+      <c r="L3" t="str">
         <v>구간별로 정의된 함수, 극한이 존재할 조건(좌극한=우극한)</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>우극한은 -x²+4에 1을 대입해 3, 좌극한은 2x+a에서 2+a → 두 값이 같다는 조건으로 a=1</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>경계에서 어느 식을 쓰는지 구분하는 것</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>12미적Ⅰ-01-01</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <v>C~B: 극한의 뜻을 알고 좌극한·우극한이 같다는 조건으로 값을 구함</v>
       </c>
-      <c r="P3" t="str">
+      <c r="Q3" t="str">
         <v>추론, 문제해결</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="R3" t="str">
         <v>구간별 식에서 좌극한과 우극한을 구분해 계산함; 극한이 존재할 조건을 식으로 세워 미정계수를 구함</v>
       </c>
-      <c r="R3" t="str">
+      <c r="S3" t="str">
         <v>구간에 따라 다르게 정의된 함수에서 좌극한과 우극한이 같아야 극한이 존재한다는 조건을 식으로 세워 미정계수를 구하는 과정을 설명함.</v>
       </c>
-      <c r="S3" t="str">
+      <c r="T3" t="str">
         <v>a=1</v>
       </c>
-      <c r="T3" t="str">
-        <v/>
-      </c>
       <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
         <v/>
       </c>
     </row>
@@ -3993,36 +4017,39 @@
         <v>두 함수의 그래프를 보고 합, 차, 곱, 몫의 극한 중 x가 2로 갈 때 극한값이 존재하는 것을 고르는 문제</v>
       </c>
       <c r="K4" t="str">
+        <v>그래프를 이용한 두 함수의 합과 곱의 극한 판정</v>
+      </c>
+      <c r="L4" t="str">
         <v>그래프에서 좌극한·우극한 읽기, 함수의 극한에 대한 성질, 각 극한이 없어도 곱·몫의 극한은 존재할 수 있음</v>
       </c>
-      <c r="L4" t="str">
+      <c r="M4" t="str">
         <v>그래프에서 f는 좌우극한 모두 0, g는 우극한 2·좌극한 1 → 합·차는 좌우가 달라 없음, 곱과 몫은 좌우 모두 0이 되어 존재 → ㄷ, ㄹ</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
         <v>극한의 성질은 각 극한이 존재할 때만 쓸 수 있다는 점, g의 극한이 없어도 fg의 극한이 존재하는 이유를 좌우극한으로 확인하는 것</v>
       </c>
-      <c r="N4" t="str">
+      <c r="O4" t="str">
         <v>12미적Ⅰ-01-01, 12미적Ⅰ-01-02</v>
       </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
         <v>B~A: 그래프에서 좌우극한을 읽고 극한의 성질이 성립할 조건을 따져 판단함</v>
       </c>
-      <c r="P4" t="str">
+      <c r="Q4" t="str">
         <v>추론, 정보처리, 의사소통</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="R4" t="str">
         <v>그래프에서 각 함수의 좌극한과 우극한을 읽어 냄; 합, 차, 곱, 몫의 좌우극한을 각각 비교해 극한의 존재를 판정함</v>
       </c>
-      <c r="R4" t="str">
+      <c r="S4" t="str">
         <v>두 함수의 그래프에서 좌극한과 우극한을 읽어 내고, 극한이 존재하지 않는 함수가 있어도 곱과 몫의 극한은 존재할 수 있음을 좌우극한을 비교해 논리적으로 설명함.</v>
       </c>
-      <c r="S4" t="str">
+      <c r="T4" t="str">
         <v>ㄷ, ㄹ</v>
       </c>
-      <c r="T4" t="str">
-        <v/>
-      </c>
       <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
         <v/>
       </c>
     </row>
@@ -4058,36 +4085,39 @@
         <v>0/0 꼴 유리식, 무리식 극한과 (0×∞) 꼴 극한값을 구하는 문제</v>
       </c>
       <c r="K5" t="str">
+        <v>인수분해와 유리화를 이용한 극한값 계산</v>
+      </c>
+      <c r="L5" t="str">
         <v>0/0 꼴 극한, 인수분해와 약분, 분모의 유리화, 식의 전개</v>
       </c>
-      <c r="L5" t="str">
+      <c r="M5" t="str">
         <v>(1) 분모를 (x-2)(x+1)로 인수분해해 약분 → 1/3 (2) √x-3을 유리화하거나 x-9=(√x-3)(√x+3)으로 약분 → 6 (3) 괄호를 전개해 (x+2)-3으로 정리 → -3</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
         <v>식의 꼴에 따라 인수분해, 유리화, 전개 중 알맞은 방법을 고르는 것</v>
       </c>
-      <c r="N5" t="str">
+      <c r="O5" t="str">
         <v>12미적Ⅰ-01-02</v>
       </c>
-      <c r="O5" t="str">
+      <c r="P5" t="str">
         <v>C~B: 극한의 성질을 이용해 여러 꼴의 극한값을 구함</v>
       </c>
-      <c r="P5" t="str">
+      <c r="Q5" t="str">
         <v>문제해결, 의사소통</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="R5" t="str">
         <v>식의 꼴을 보고 인수분해, 유리화, 전개 중 알맞은 방법을 골라 극한값을 구함; 각 소문항의 풀이 과정을 단계별로 설명함</v>
       </c>
-      <c r="R5" t="str">
+      <c r="S5" t="str">
         <v>0/0 꼴의 극한을 인수분해와 유리화로 정리하는 등 식의 꼴에 맞는 방법을 골라 극한값을 구하고, 그 과정을 단계별로 설명함.</v>
       </c>
-      <c r="S5" t="str">
+      <c r="T5" t="str">
         <v>(1) 1/3 (2) 6 (3) -3</v>
       </c>
-      <c r="T5" t="str">
-        <v/>
-      </c>
       <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
         <v/>
       </c>
     </row>
@@ -4123,36 +4153,39 @@
         <v>x가 음의 무한대, 양의 무한대로 갈 때 ∞/∞ 꼴 극한값을 구하는 문제(절댓값, 근호 포함)</v>
       </c>
       <c r="K6" t="str">
+        <v>무한대로 발산하는 분수식의 극한값 계산</v>
+      </c>
+      <c r="L6" t="str">
         <v>∞/∞ 꼴 극한, 최고차항으로 나누기, x&lt;0일 때 |x|=-x, 근호 안의 식 정리</v>
       </c>
-      <c r="L6" t="str">
+      <c r="M6" t="str">
         <v>(1) x→-∞이므로 |x|=-x로 바꾸고 분자·분모를 x로 나눔 → -1 (2) 분자·분모를 x로 나누고 √(x²+1)/x=√(1+1/x²)로 정리 → 3</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
         <v>x→-∞에서 절댓값의 부호 처리, 근호 안으로 x를 넣을 때의 부호</v>
       </c>
-      <c r="N6" t="str">
+      <c r="O6" t="str">
         <v>12미적Ⅰ-01-02</v>
       </c>
-      <c r="O6" t="str">
+      <c r="P6" t="str">
         <v>B: 주어진 조건(x의 부호)을 고려해 ∞/∞ 꼴 극한값을 구함</v>
       </c>
-      <c r="P6" t="str">
+      <c r="Q6" t="str">
         <v>문제해결, 추론</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="R6" t="str">
         <v>x가 음의 무한대로 갈 때 절댓값을 부호에 맞게 바꿈; 분자와 분모를 최고차항으로 나누어 극한값을 구하고 이유를 설명함</v>
       </c>
-      <c r="R6" t="str">
+      <c r="S6" t="str">
         <v>∞/∞ 꼴의 극한에서 x의 부호에 따라 절댓값과 근호를 바르게 정리하고, 분자와 분모를 최고차항으로 나누어 극한값을 구하는 과정을 설명함.</v>
       </c>
-      <c r="S6" t="str">
+      <c r="T6" t="str">
         <v>(1) -1 (2) 3</v>
       </c>
-      <c r="T6" t="str">
-        <v/>
-      </c>
       <c r="U6" t="str">
+        <v/>
+      </c>
+      <c r="V6" t="str">
         <v/>
       </c>
     </row>
@@ -4188,36 +4221,39 @@
         <v>두 무리식의 차(∞-∞ 꼴)의 극한값이 5가 되도록 미정계수를 정하는 문제</v>
       </c>
       <c r="K7" t="str">
+        <v>무리식의 차의 극한을 이용한 미정계수 결정</v>
+      </c>
+      <c r="L7" t="str">
         <v>∞-∞ 꼴 극한, 분자의 유리화, 극한값을 이용한 미정계수 결정</v>
       </c>
-      <c r="L7" t="str">
+      <c r="M7" t="str">
         <v>분자를 유리화해 ((a-1)x+2)/(√(x²+ax+4)+√(x²+x+2))로 바꿈 → x로 나누면 극한값은 (a-1)/2 → (a-1)/2=5에서 a=11</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
         <v>∞-∞ 꼴을 유리화로 ∞/∞ 꼴로 바꾸는 발상, 극한값 조건을 방정식으로 연결하는 것</v>
       </c>
-      <c r="N7" t="str">
+      <c r="O7" t="str">
         <v>12미적Ⅰ-01-02</v>
       </c>
-      <c r="O7" t="str">
+      <c r="P7" t="str">
         <v>B~A: 극한의 성질을 활용해 극한값 조건에서 미정계수를 구함</v>
       </c>
-      <c r="P7" t="str">
+      <c r="Q7" t="str">
         <v>문제해결, 추론</v>
       </c>
-      <c r="Q7" t="str">
+      <c r="R7" t="str">
         <v>∞-∞ 꼴을 유리화하여 ∞/∞ 꼴로 바꿈; 구한 극한값을 주어진 조건과 연결해 미정계수를 구함</v>
       </c>
-      <c r="R7" t="str">
+      <c r="S7" t="str">
         <v>∞-∞ 꼴의 무리식 극한을 유리화하여 계산 가능한 꼴로 바꾸고, 극한값 조건을 방정식으로 세워 미정계수를 구하는 과정을 논리적으로 설명함.</v>
       </c>
-      <c r="S7" t="str">
+      <c r="T7" t="str">
         <v>a=11</v>
       </c>
-      <c r="T7" t="str">
-        <v/>
-      </c>
       <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
         <v/>
       </c>
     </row>
@@ -4253,36 +4289,39 @@
         <v>f(x)/x의 극한이 존재한다는 조건으로 f(x)를 포함한 분수식의 극한값을 구하는 문제</v>
       </c>
       <c r="K8" t="str">
+        <v>극한 조건을 변형한 함수의 극한값 계산</v>
+      </c>
+      <c r="L8" t="str">
         <v>함수의 극한에 대한 성질, f(x)/x가 수렴하면 f(x)/x²은 0으로 수렴</v>
       </c>
-      <c r="L8" t="str">
+      <c r="M8" t="str">
         <v>분자·분모를 x²으로 나눔 → f(x)/x² = (f(x)/x)·(1/x) → 0 → 극한값 3</v>
       </c>
-      <c r="M8" t="str">
+      <c r="N8" t="str">
         <v>f(x)의 식을 모르는 상태에서 주어진 극한 조건을 변형해 쓰는 것</v>
       </c>
-      <c r="N8" t="str">
+      <c r="O8" t="str">
         <v>12미적Ⅰ-01-02</v>
       </c>
-      <c r="O8" t="str">
+      <c r="P8" t="str">
         <v>A: 극한의 성질을 설명하고 식이 주어지지 않은 함수에 활용함</v>
       </c>
-      <c r="P8" t="str">
+      <c r="Q8" t="str">
         <v>추론, 문제해결</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="R8" t="str">
         <v>구체적인 식이 없는 함수의 극한 조건을 변형해 활용함; 분자와 분모를 x²으로 나누는 이유와 각 항의 극한을 설명함</v>
       </c>
-      <c r="R8" t="str">
+      <c r="S8" t="str">
         <v>식이 주어지지 않은 함수에 대해 주어진 극한 조건을 변형하여 극한의 성질을 적용하고, 각 항이 수렴하는 이유를 근거를 들어 설명함.</v>
       </c>
-      <c r="S8" t="str">
+      <c r="T8" t="str">
         <v>3</v>
       </c>
-      <c r="T8" t="str">
-        <v/>
-      </c>
       <c r="U8" t="str">
+        <v/>
+      </c>
+      <c r="V8" t="str">
         <v/>
       </c>
     </row>
@@ -4318,36 +4357,39 @@
         <v>0/0 꼴 극한값이 주어졌을 때 유리식, 무리식의 미정계수 a, b를 구하는 문제</v>
       </c>
       <c r="K9" t="str">
+        <v>극한값이 존재할 조건을 이용한 미정계수 결정</v>
+      </c>
+      <c r="L9" t="str">
         <v>분모가 0으로 가고 극한값이 존재하면 분자도 0으로 감, 인수분해, 분모의 유리화</v>
       </c>
-      <c r="L9" t="str">
+      <c r="M9" t="str">
         <v>(1) 분자에 x=1 대입해 a+b-1=0 → 분자를 (x-1)(ax+1)로 인수분해 → a+1=2 → a=1, b=0 (2) 4a+b=0 → 분자 a(x-4), 분모 유리화 → 2√5a=√5 → a=1/2, b=-2</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
         <v>"분모→0이면 분자→0"이라는 필요조건을 찾는 것, 조건을 대입한 뒤 식을 다시 정리하는 것</v>
       </c>
-      <c r="N9" t="str">
+      <c r="O9" t="str">
         <v>12미적Ⅰ-01-02</v>
       </c>
-      <c r="O9" t="str">
+      <c r="P9" t="str">
         <v>B~A: 극한값이 존재할 조건을 이용해 미정계수를 구하고 그 이유를 설명함</v>
       </c>
-      <c r="P9" t="str">
+      <c r="Q9" t="str">
         <v>추론, 문제해결, 의사소통</v>
       </c>
-      <c r="Q9" t="str">
+      <c r="R9" t="str">
         <v>분모가 0으로 갈 때 분자도 0으로 가야 하는 이유를 설명함; 조건을 대입해 식을 인수분해하거나 유리화하여 미정계수를 구함</v>
       </c>
-      <c r="R9" t="str">
+      <c r="S9" t="str">
         <v>분모가 0으로 갈 때 극한값이 존재하려면 분자도 0으로 가야 함을 설명하고, 이 조건과 인수분해, 유리화를 이용해 미정계수를 차례로 구함.</v>
       </c>
-      <c r="S9" t="str">
+      <c r="T9" t="str">
         <v>(1) a=1, b=0 (2) a=1/2, b=-2</v>
       </c>
-      <c r="T9" t="str">
-        <v/>
-      </c>
       <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
         <v/>
       </c>
     </row>
@@ -4383,36 +4425,39 @@
         <v>부등식으로 범위가 주어진 함수 f(x)에 대해 {f(x)}²을 포함한 식의 극한값을 구하는 문제</v>
       </c>
       <c r="K10" t="str">
+        <v>함수의 극한의 대소 관계를 이용한 극한값 계산</v>
+      </c>
+      <c r="L10" t="str">
         <v>함수의 극한의 대소 관계(조임 정리), 부등식의 변형</v>
       </c>
-      <c r="L10" t="str">
+      <c r="M10" t="str">
         <v>부등식을 x(x+1)로 나누어 (2x²-x)/(x(x+1)) &lt; f(x)/x &lt; (2x²+x)/(x(x+1)) → 양쪽 극한 2 → f(x)/x→2 → 식을 x²으로 나누면 4/2=2</v>
       </c>
-      <c r="M10" t="str">
+      <c r="N10" t="str">
         <v>부등식을 극한을 구하기 좋은 꼴로 나누는 것, 조임 정리로 얻은 결과를 원래 식에 연결하는 것</v>
       </c>
-      <c r="N10" t="str">
+      <c r="O10" t="str">
         <v>12미적Ⅰ-01-02</v>
       </c>
-      <c r="O10" t="str">
+      <c r="P10" t="str">
         <v>A: 극한의 대소 관계를 활용해 식을 모르는 함수의 극한을 구하고 과정을 설명함</v>
       </c>
-      <c r="P10" t="str">
+      <c r="Q10" t="str">
         <v>추론, 문제해결, 연결</v>
       </c>
-      <c r="Q10" t="str">
+      <c r="R10" t="str">
         <v>부등식을 알맞게 변형해 양쪽의 극한을 구함; 함수의 극한의 대소 관계를 적용해 극한값을 구하는 근거를 설명함</v>
       </c>
-      <c r="R10" t="str">
+      <c r="S10" t="str">
         <v>부등식으로만 주어진 함수에 대해 부등식을 알맞게 변형하고 함수의 극한의 대소 관계를 적용하여 극한값을 구하는 과정을 논리적으로 설명함.</v>
       </c>
-      <c r="S10" t="str">
+      <c r="T10" t="str">
         <v>2</v>
       </c>
-      <c r="T10" t="str">
-        <v/>
-      </c>
       <c r="U10" t="str">
+        <v/>
+      </c>
+      <c r="V10" t="str">
         <v/>
       </c>
     </row>
@@ -4448,36 +4493,39 @@
         <v>직선과 원의 교점 P에서 x축에 내린 수선의 발 H에 대해 두 선분 길이의 곱 OA×PH의 극한을 구하는 문제</v>
       </c>
       <c r="K11" t="str">
+        <v>원과 직선의 교점을 이용한 선분 길이의 극한</v>
+      </c>
+      <c r="L11" t="str">
         <v>직선과 원의 교점, 좌표로 선분의 길이 나타내기, ∞/∞ 꼴 극한</v>
       </c>
-      <c r="L11" t="str">
+      <c r="M11" t="str">
         <v>직선 y=t(x+1)과 원을 연립 → x=-1이 아닌 교점 P((1-t²)/(1+t²), 2t/(1+t²)) → OA=t, PH=2t/(1+t²) → 곱 2t²/(1+t²)의 극한 2</v>
       </c>
-      <c r="M11" t="str">
+      <c r="N11" t="str">
         <v>도형 조건을 좌표와 식으로 옮기는 것, x=-1이 한 근임을 이용해 이차방정식을 인수분해하는 것</v>
       </c>
-      <c r="N11" t="str">
+      <c r="O11" t="str">
         <v>12미적Ⅰ-01-02</v>
       </c>
-      <c r="O11" t="str">
+      <c r="P11" t="str">
         <v>A: 극한의 성질을 도형 문제에 활용하고 그 과정을 설명함</v>
       </c>
-      <c r="P11" t="str">
+      <c r="Q11" t="str">
         <v>문제해결, 연결, 의사소통</v>
       </c>
-      <c r="Q11" t="str">
+      <c r="R11" t="str">
         <v>도형의 조건을 좌표와 식으로 나타냄; 교점의 좌표를 구해 선분의 길이를 변수에 대한 식으로 세움; 극한값을 구하는 과정을 단계별로 설명함</v>
       </c>
-      <c r="R11" t="str">
+      <c r="S11" t="str">
         <v>원과 직선의 교점 조건을 좌표로 나타내 선분의 길이를 변수에 대한 식으로 세우고, 극한의 성질을 활용해 값을 구하는 과정을 그림과 연결하여 논리적으로 설명함.</v>
       </c>
-      <c r="S11" t="str">
+      <c r="T11" t="str">
         <v>2</v>
       </c>
-      <c r="T11" t="str">
-        <v/>
-      </c>
       <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
         <v/>
       </c>
     </row>
@@ -4513,42 +4561,45 @@
         <v>극한값이 존재한다는 조건과 다항함수 사이의 관계식을 이용해 f(x)g(x)/(x²-4)의 극한값을 구하는 문제</v>
       </c>
       <c r="K12" t="str">
+        <v>극한 조건과 다항함수의 관계식을 이용한 극한값 계산</v>
+      </c>
+      <c r="L12" t="str">
         <v>극한값이 존재할 조건(분모→0이면 분자→0), 다항식의 인수, 함숫값 결정</v>
       </c>
-      <c r="L12" t="str">
+      <c r="M12" t="str">
         <v>첫 조건에서 g(2)=4 → 관계식에서 f(x)=(x-2){g(x)-(x-2)} → 약분하면 {g(x)-x+2}g(x)/(x+2) → x=2 대입해 4·4/4=4</v>
       </c>
-      <c r="M12" t="str">
+      <c r="N12" t="str">
         <v>두 조건을 연결해 f(x)가 (x-2)를 인수로 가짐을 찾는 것, 구체적인 식 없이 함숫값만으로 극한을 계산하는 것</v>
       </c>
-      <c r="N12" t="str">
+      <c r="O12" t="str">
         <v>12미적Ⅰ-01-02</v>
       </c>
-      <c r="O12" t="str">
+      <c r="P12" t="str">
         <v>A: 극한의 성질과 다항식의 성질을 함께 활용해 복합적인 문제를 해결하고 설명함</v>
       </c>
-      <c r="P12" t="str">
+      <c r="Q12" t="str">
         <v>추론, 연결, 문제해결</v>
       </c>
-      <c r="Q12" t="str">
+      <c r="R12" t="str">
         <v>극한값이 존재할 조건에서 함숫값을 찾아냄; 관계식을 변형해 다항함수의 인수를 찾고 약분하여 극한값을 구함; 두 조건을 연결하는 근거를 설명함</v>
       </c>
-      <c r="R12" t="str">
+      <c r="S12" t="str">
         <v>극한값이 존재할 조건에서 함숫값을 찾아내고, 다항함수 사이의 관계식을 변형해 공통인수를 찾아 약분하는 등 여러 조건을 연결하여 극한값을 구하는 과정을 설명함.</v>
       </c>
-      <c r="S12" t="str">
+      <c r="T12" t="str">
         <v>4</v>
       </c>
-      <c r="T12" t="str">
-        <v/>
-      </c>
       <c r="U12" t="str">
+        <v/>
+      </c>
+      <c r="V12" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V12"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4556,6 +4607,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D21"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="12"/>
+    <col min="2" max="2" customWidth="1" width="22"/>
+    <col min="3" max="3" customWidth="1" width="16"/>
+    <col min="4" max="4" customWidth="1" width="80"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4863,6 +4920,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D6"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="12"/>
+    <col min="2" max="2" customWidth="1" width="10"/>
+    <col min="3" max="3" customWidth="1" width="10"/>
+    <col min="4" max="4" customWidth="1" width="90"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4960,6 +5023,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B26"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="90"/>
+    <col min="2" max="2" customWidth="1" width="24"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
